--- a/docs/dev/farmguardian_backlog_FE.xlsx
+++ b/docs/dev/farmguardian_backlog_FE.xlsx
@@ -105,7 +105,7 @@
     <t>온보딩</t>
   </si>
   <si>
-    <t>카카오 SSO 로그인 구현</t>
+    <t>가입·로그인 화면 구현 (필지 선택 포함)</t>
   </si>
   <si>
     <t>S3</t>

--- a/docs/dev/farmguardian_backlog_FE.xlsx
+++ b/docs/dev/farmguardian_backlog_FE.xlsx
@@ -84,7 +84,7 @@
     <t>FE-03</t>
   </si>
   <si>
-    <t>API 연동 공통 처리 (토큰·에러)</t>
+    <t>API 연동 공통 처리 (X-User-Id·에러)</t>
   </si>
   <si>
     <t>FE-04</t>
